--- a/data/trans_orig/barthel_r-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/barthel_r-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según grado de dependencia funcional para actividades básicas de la vida diaria (Barthel) en 2007</t>
+          <t>Población según el grado de dependencia funcional para actividades básicas de la vida diaria (Barthel) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89139</t>
+          <t>88300</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>103791</t>
+          <t>103552</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>113514</t>
+          <t>113026</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132354</t>
+          <t>132447</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>207917</t>
+          <t>208474</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>232289</t>
+          <t>231978</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,7%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11376</t>
+          <t>11401</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17361</t>
+          <t>17109</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>8184</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23949</t>
+          <t>23045</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15396</t>
+          <t>15701</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>16783</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10805</t>
+          <t>10585</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27599</t>
+          <t>27749</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8890</t>
+          <t>8680</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10187</t>
+          <t>10844</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14726</t>
+          <t>15603</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -1185,97 +1185,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2343</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1837</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7868</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>2343</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>8061</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>8240</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2343</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>7017</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113880</t>
+          <t>113780</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130850</t>
+          <t>131588</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>126686</t>
+          <t>127198</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>150834</t>
+          <t>151945</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>250495</t>
+          <t>249263</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>279341</t>
+          <t>278046</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,62%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19279</t>
+          <t>17640</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24571</t>
+          <t>23597</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16990</t>
+          <t>16980</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36959</t>
+          <t>36048</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13029</t>
+          <t>14393</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11237</t>
+          <t>11937</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29098</t>
+          <t>30063</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16530</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37444</t>
+          <t>38093</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10691</t>
+          <t>11560</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15575</t>
+          <t>15475</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21383</t>
+          <t>21240</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85615</t>
+          <t>85332</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98168</t>
+          <t>98189</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99935</t>
+          <t>101069</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>118337</t>
+          <t>118867</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>191925</t>
+          <t>190903</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>213661</t>
+          <t>213111</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,71%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15445</t>
+          <t>14655</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17686</t>
+          <t>16598</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>10283</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26183</t>
+          <t>26736</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7311</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15733</t>
+          <t>14989</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5754</t>
+          <t>6071</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19033</t>
+          <t>18905</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15422</t>
+          <t>14246</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>4199</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15691</t>
+          <t>16364</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -2549,97 +2549,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1942</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1848</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>113547</t>
+          <t>113842</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>128031</t>
+          <t>127456</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>151387</t>
+          <t>151397</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>175148</t>
+          <t>174443</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>269857</t>
+          <t>269375</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>298259</t>
+          <t>298006</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,13%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>822</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>7029</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22757</t>
+          <t>20784</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>26050</t>
+          <t>25982</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17313</t>
+          <t>16603</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15383</t>
+          <t>15639</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33945</t>
+          <t>34408</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>22265</t>
+          <t>23424</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>45401</t>
+          <t>46548</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2329</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12842</t>
+          <t>14078</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>14804</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>840</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>419791</t>
+          <t>419306</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>448523</t>
+          <t>448807</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>515980</t>
+          <t>515934</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>559922</t>
+          <t>558877</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>945972</t>
+          <t>948060</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>997871</t>
+          <t>1000478</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,84%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18123</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38003</t>
+          <t>38309</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>34004</t>
+          <t>34567</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>60613</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>58003</t>
+          <t>59018</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>92077</t>
+          <t>91617</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19698</t>
+          <t>19444</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>39347</t>
+          <t>40544</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>45484</t>
+          <t>46902</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>77081</t>
+          <t>77364</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>71283</t>
+          <t>70831</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>107950</t>
+          <t>108646</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18651</t>
+          <t>19371</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17208</t>
+          <t>17360</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>38281</t>
+          <t>39391</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>26404</t>
+          <t>26568</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>51787</t>
+          <t>51851</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10513</t>
+          <t>10434</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11122</t>
+          <t>12129</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según grado de dependencia funcional para actividades básicas de la vida diaria (Barthel) en 2012</t>
+          <t>Población según el grado de dependencia funcional para actividades básicas de la vida diaria (Barthel) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112992</t>
+          <t>112231</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>127702</t>
+          <t>128143</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>102680</t>
+          <t>103105</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>126511</t>
+          <t>127087</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>220524</t>
+          <t>219189</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>250257</t>
+          <t>248856</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,24%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>12792</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18585</t>
+          <t>18395</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9524</t>
+          <t>10192</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26939</t>
+          <t>27081</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14763</t>
+          <t>15554</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20835</t>
+          <t>20464</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40241</t>
+          <t>40403</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27199</t>
+          <t>27426</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51763</t>
+          <t>50835</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16120</t>
+          <t>17081</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>18688</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7318</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7084</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>103834</t>
+          <t>102444</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127352</t>
+          <t>126786</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>106741</t>
+          <t>105475</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>134475</t>
+          <t>134546</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>216429</t>
+          <t>216569</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>253549</t>
+          <t>253647</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,25%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14667</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17098</t>
+          <t>16379</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>8565</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25896</t>
+          <t>26532</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14091</t>
+          <t>14723</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33941</t>
+          <t>34021</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30800</t>
+          <t>30904</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>54113</t>
+          <t>55358</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>51191</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>82774</t>
+          <t>81527</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14190</t>
+          <t>13966</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8995</t>
+          <t>9294</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24071</t>
+          <t>25072</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14669</t>
+          <t>14545</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33594</t>
+          <t>33478</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>981</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>10136</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15049</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71530</t>
+          <t>72748</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91803</t>
+          <t>91190</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>84839</t>
+          <t>85723</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108115</t>
+          <t>107846</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>164107</t>
+          <t>163953</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>194911</t>
+          <t>194659</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,58%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11574</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>965</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15528</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19677</t>
+          <t>18474</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18688</t>
+          <t>18775</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38635</t>
+          <t>39454</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>27098</t>
+          <t>27171</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>51705</t>
+          <t>50651</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13939</t>
+          <t>13834</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14427</t>
+          <t>16087</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>7525</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22275</t>
+          <t>23915</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12214</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>984</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13024</t>
+          <t>12551</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>122086</t>
+          <t>121890</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>142988</t>
+          <t>142569</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>162122</t>
+          <t>160998</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>189207</t>
+          <t>189549</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>289599</t>
+          <t>292713</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>324680</t>
+          <t>327093</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,69%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9835</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12524</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28712</t>
+          <t>28973</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>15832</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>34200</t>
+          <t>34734</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25817</t>
+          <t>24348</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24515</t>
+          <t>23361</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46406</t>
+          <t>45563</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>37680</t>
+          <t>36666</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>65960</t>
+          <t>64691</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16191</t>
+          <t>14453</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18666</t>
+          <t>18995</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10642</t>
+          <t>10353</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>27687</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -6878,7 +6878,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9681</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11530</t>
+          <t>11722</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>433822</t>
+          <t>432743</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>473792</t>
+          <t>473497</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>481367</t>
+          <t>482401</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>534906</t>
+          <t>531881</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>930471</t>
+          <t>931368</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>995139</t>
+          <t>996504</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,5%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14275</t>
+          <t>13814</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>33088</t>
+          <t>33858</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>31953</t>
+          <t>29989</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>57128</t>
+          <t>55252</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>49046</t>
+          <t>47887</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>82225</t>
+          <t>81381</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>42597</t>
+          <t>42738</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>72331</t>
+          <t>72738</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>113781</t>
+          <t>115387</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>155774</t>
+          <t>157887</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>162301</t>
+          <t>163434</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>215919</t>
+          <t>217574</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13608</t>
+          <t>13182</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>34847</t>
+          <t>32361</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>32027</t>
+          <t>31199</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>56993</t>
+          <t>58573</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>48274</t>
+          <t>49309</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>82199</t>
+          <t>83470</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12426</t>
+          <t>12546</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>8717</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25895</t>
+          <t>25525</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>13720</t>
+          <t>13845</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>33658</t>
+          <t>32420</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según grado de dependencia funcional para actividades básicas de la vida diaria (Barthel) en 2016</t>
+          <t>Población según el grado de dependencia funcional para actividades básicas de la vida diaria (Barthel) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>102742</t>
+          <t>103773</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>120452</t>
+          <t>119956</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>103501</t>
+          <t>103044</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>129248</t>
+          <t>129489</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>215250</t>
+          <t>214040</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>246098</t>
+          <t>244571</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>78,86%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10069</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>8949</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24692</t>
+          <t>25251</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12227</t>
+          <t>12660</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30049</t>
+          <t>29895</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16819</t>
+          <t>15885</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23522</t>
+          <t>23564</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45731</t>
+          <t>47842</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32157</t>
+          <t>32240</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56557</t>
+          <t>57177</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15931</t>
+          <t>16920</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13437</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25011</t>
+          <t>23285</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>5888</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7246</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>123783</t>
+          <t>125264</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143095</t>
+          <t>143876</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>139523</t>
+          <t>139057</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>168923</t>
+          <t>168156</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>271610</t>
+          <t>271146</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>308274</t>
+          <t>307290</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,0%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17442</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16093</t>
+          <t>15558</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36163</t>
+          <t>35246</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23114</t>
+          <t>22444</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47592</t>
+          <t>45951</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>22831</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17987</t>
+          <t>19573</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40458</t>
+          <t>42550</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30693</t>
+          <t>30768</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57281</t>
+          <t>56854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10372</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17446</t>
+          <t>17766</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>7098</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22668</t>
+          <t>23971</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10333</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12729</t>
+          <t>12875</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85769</t>
+          <t>85861</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101863</t>
+          <t>101960</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>84393</t>
+          <t>82178</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107676</t>
+          <t>107212</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>175662</t>
+          <t>174787</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>205850</t>
+          <t>204471</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,37%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15726</t>
+          <t>14945</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17008</t>
+          <t>17140</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>9289</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27219</t>
+          <t>27492</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17107</t>
+          <t>16643</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14660</t>
+          <t>15824</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35104</t>
+          <t>35777</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>23551</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>47567</t>
+          <t>46397</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7656</t>
+          <t>7429</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17065</t>
+          <t>17141</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6149</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22634</t>
+          <t>20932</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>9648</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10446</t>
+          <t>9268</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>139258</t>
+          <t>138961</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>157164</t>
+          <t>157488</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>152856</t>
+          <t>152843</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>183691</t>
+          <t>184840</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>298987</t>
+          <t>300396</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>335484</t>
+          <t>337024</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,74%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15492</t>
+          <t>15606</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13597</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33472</t>
+          <t>33128</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20966</t>
+          <t>20860</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>43504</t>
+          <t>43798</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7668</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21151</t>
+          <t>22576</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30416</t>
+          <t>29301</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>58154</t>
+          <t>57487</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>41396</t>
+          <t>41479</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>70777</t>
+          <t>72038</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>786</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15721</t>
+          <t>15847</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20799</t>
+          <t>20741</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -10515,82 +10515,82 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>1754</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>4991</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>1233</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>6272</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1233</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>472427</t>
+          <t>471946</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>506998</t>
+          <t>507409</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>513583</t>
+          <t>507130</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>566371</t>
+          <t>562905</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>993134</t>
+          <t>992970</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1059730</t>
+          <t>1059815</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,4%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21383</t>
+          <t>21090</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42378</t>
+          <t>41954</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>55599</t>
+          <t>55552</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>90629</t>
+          <t>90654</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,7 +10908,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>81973</t>
+          <t>83549</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>123467</t>
+          <t>124715</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>34979</t>
+          <t>35038</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>59569</t>
+          <t>61410</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>106545</t>
+          <t>107238</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>152742</t>
+          <t>154483</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>147680</t>
+          <t>149103</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>203386</t>
+          <t>200783</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14089</t>
+          <t>13756</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>30467</t>
+          <t>30993</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>20411</t>
+          <t>21601</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>46459</t>
+          <t>46110</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>38203</t>
+          <t>39528</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>68458</t>
+          <t>67937</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>821</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>19466</t>
+          <t>18940</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6084</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>22016</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según grado de dependencia funcional para actividades básicas de la vida diaria (Barthel) en 2023</t>
+          <t>Población según el grado de dependencia funcional para actividades básicas de la vida diaria (Barthel) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>104498</t>
+          <t>104603</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>120250</t>
+          <t>121262</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>98001</t>
+          <t>97499</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114251</t>
+          <t>113597</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>207077</t>
+          <t>205882</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>230306</t>
+          <t>229989</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,84%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8954</t>
+          <t>8867</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19763</t>
+          <t>20198</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20494</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32683</t>
+          <t>32720</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32850</t>
+          <t>33010</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48445</t>
+          <t>48692</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20443</t>
+          <t>20994</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24829</t>
+          <t>25195</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38107</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,47 +11935,47 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
+          <t>14,17%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>21,43%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>45328</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>37243</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>54111</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
           <t>13,96%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>21,66%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>45328</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>36827</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>54621</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>13,96%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>9920</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18025</t>
+          <t>17969</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12918</t>
+          <t>12826</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24407</t>
+          <t>25162</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>709</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4292</t>
+          <t>4770</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>120123</t>
+          <t>118568</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>135685</t>
+          <t>134945</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>129866</t>
+          <t>130356</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149739</t>
+          <t>149957</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>255435</t>
+          <t>254478</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>280615</t>
+          <t>279750</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,19%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11812</t>
+          <t>11468</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19176</t>
+          <t>18618</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31847</t>
+          <t>31995</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24266</t>
+          <t>25098</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39930</t>
+          <t>41173</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11835</t>
+          <t>11599</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23667</t>
+          <t>23996</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25459</t>
+          <t>25857</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39856</t>
+          <t>40326</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39922</t>
+          <t>40941</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>58527</t>
+          <t>59353</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12512</t>
+          <t>12676</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11968</t>
+          <t>11979</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23486</t>
+          <t>24864</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12735,7 +12735,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>18391</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33368</t>
+          <t>33153</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2397</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12813,7 +12813,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>898</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5793</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95705</t>
+          <t>94732</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112200</t>
+          <t>111965</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>227615</t>
+          <t>223884</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>343530</t>
+          <t>344871</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>341128</t>
+          <t>340388</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>466946</t>
+          <t>466075</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>11342</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24425</t>
+          <t>24578</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6902</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57016</t>
+          <t>58183</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11613</t>
+          <t>13931</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73180</t>
+          <t>72760</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18845</t>
+          <t>19354</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>5840</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55894</t>
+          <t>58582</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12300</t>
+          <t>11355</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64180</t>
+          <t>64070</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>854</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7543</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1692</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23787</t>
+          <t>23642</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23762</t>
+          <t>23936</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -13475,97 +13475,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1354</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5133</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>738</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>3498</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>738</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>5028</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>152892</t>
+          <t>152589</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>170372</t>
+          <t>170472</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>159660</t>
+          <t>158859</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>182649</t>
+          <t>181621</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>316692</t>
+          <t>318211</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>347798</t>
+          <t>347165</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12402</t>
+          <t>12502</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24772</t>
+          <t>25597</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35176</t>
+          <t>35063</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>52624</t>
+          <t>52987</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>50988</t>
+          <t>51313</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>74220</t>
+          <t>72783</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14748</t>
+          <t>14703</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28430</t>
+          <t>28172</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>33161</t>
+          <t>34292</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50691</t>
+          <t>50332</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>51497</t>
+          <t>51774</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>73106</t>
+          <t>74754</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22112</t>
+          <t>22549</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13190</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26348</t>
+          <t>26878</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>781</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>432</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4769</t>
+          <t>4661</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>491576</t>
+          <t>489981</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>525652</t>
+          <t>524257</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>637663</t>
+          <t>638243</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>858654</t>
+          <t>867480</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1161224</t>
+          <t>1155685</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1360846</t>
+          <t>1391367</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>83,01%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>44723</t>
+          <t>45396</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>67930</t>
+          <t>69212</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>61537</t>
+          <t>59944</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>152980</t>
+          <t>153666</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>118510</t>
+          <t>111567</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>202567</t>
+          <t>207125</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>53520</t>
+          <t>54274</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>78398</t>
+          <t>77577</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>69700</t>
+          <t>67004</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>165784</t>
+          <t>165246</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>134548</t>
+          <t>124199</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>225465</t>
+          <t>228459</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13166</t>
+          <t>12790</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26829</t>
+          <t>27204</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>29422</t>
+          <t>27247</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>73678</t>
+          <t>72920</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>50368</t>
+          <t>48494</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>90626</t>
+          <t>91116</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>338</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14859,7 +14859,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10537</t>
+          <t>11437</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12724</t>
+          <t>11732</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14929,7 +14929,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/barthel_r-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/barthel_r-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88300</t>
+          <t>89127</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>103552</t>
+          <t>103796</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>113026</t>
+          <t>113475</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132447</t>
+          <t>132520</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>208474</t>
+          <t>206240</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>231978</t>
+          <t>231146</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,38%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11401</t>
+          <t>11076</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>5097</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17109</t>
+          <t>17588</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23045</t>
+          <t>24453</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15701</t>
+          <t>15452</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16783</t>
+          <t>17104</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10585</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27749</t>
+          <t>28289</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>876</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8680</t>
+          <t>8258</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10844</t>
+          <t>10233</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15603</t>
+          <t>17070</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>7253</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113780</t>
+          <t>113371</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131588</t>
+          <t>130723</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127198</t>
+          <t>127810</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>151945</t>
+          <t>153067</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>249263</t>
+          <t>248538</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>278046</t>
+          <t>276779</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,24%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17640</t>
+          <t>18066</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23597</t>
+          <t>24247</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16980</t>
+          <t>17361</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36048</t>
+          <t>36317</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14393</t>
+          <t>14164</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>11131</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30063</t>
+          <t>29946</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>17475</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38093</t>
+          <t>38377</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1808</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>10129</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>15720</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21240</t>
+          <t>22109</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85332</t>
+          <t>86015</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98189</t>
+          <t>98699</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>101069</t>
+          <t>99363</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>118867</t>
+          <t>118308</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>190903</t>
+          <t>190594</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>213111</t>
+          <t>213410</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,84%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14655</t>
+          <t>14255</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4556</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16598</t>
+          <t>16993</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10283</t>
+          <t>10600</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26736</t>
+          <t>26261</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>877</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7361</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14989</t>
+          <t>16704</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>5885</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18905</t>
+          <t>19701</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>4946</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14246</t>
+          <t>13980</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16364</t>
+          <t>16308</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>113842</t>
+          <t>113818</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>127456</t>
+          <t>128039</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>151397</t>
+          <t>151280</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>174443</t>
+          <t>175345</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>269375</t>
+          <t>270859</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>298006</t>
+          <t>299653</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,61%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>825</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8173</t>
+          <t>7737</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>7176</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20784</t>
+          <t>22608</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25982</t>
+          <t>25550</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16603</t>
+          <t>16926</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15639</t>
+          <t>14674</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34408</t>
+          <t>33126</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>23424</t>
+          <t>23608</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>46548</t>
+          <t>46821</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5919</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2253</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>13360</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14804</t>
+          <t>14848</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>832</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>419306</t>
+          <t>418670</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>448807</t>
+          <t>447671</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>515934</t>
+          <t>514436</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>558877</t>
+          <t>558410</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>948060</t>
+          <t>948531</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1000478</t>
+          <t>1000839</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17645</t>
+          <t>19008</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38309</t>
+          <t>38177</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>34567</t>
+          <t>34970</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>61542</t>
+          <t>61466</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>59018</t>
+          <t>56690</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>91617</t>
+          <t>89687</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19444</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40544</t>
+          <t>41248</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>46902</t>
+          <t>47001</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>77364</t>
+          <t>76922</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>70831</t>
+          <t>71013</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>108646</t>
+          <t>108104</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6364</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>18223</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17360</t>
+          <t>18312</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>39391</t>
+          <t>39238</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>26568</t>
+          <t>26826</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>51851</t>
+          <t>50319</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12129</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112231</t>
+          <t>112296</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128143</t>
+          <t>128181</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>103105</t>
+          <t>102847</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127087</t>
+          <t>126439</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>219189</t>
+          <t>217925</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>248856</t>
+          <t>249272</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,37%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12792</t>
+          <t>12957</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18395</t>
+          <t>19225</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10192</t>
+          <t>9722</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27081</t>
+          <t>25659</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15554</t>
+          <t>14800</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20464</t>
+          <t>20208</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27426</t>
+          <t>28249</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>50835</t>
+          <t>52225</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17081</t>
+          <t>16973</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18688</t>
+          <t>19862</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>11317</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102444</t>
+          <t>102964</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>126786</t>
+          <t>126933</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>105475</t>
+          <t>106404</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>134546</t>
+          <t>133071</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>216569</t>
+          <t>218112</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>253647</t>
+          <t>253304</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,15%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15153</t>
+          <t>14773</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16379</t>
+          <t>16160</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8565</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26532</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14723</t>
+          <t>14378</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34021</t>
+          <t>33977</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30904</t>
+          <t>30840</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55358</t>
+          <t>54810</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>51191</t>
+          <t>50751</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>81527</t>
+          <t>80325</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3161</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13966</t>
+          <t>13806</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9294</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25072</t>
+          <t>24513</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14545</t>
+          <t>14569</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33478</t>
+          <t>34432</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>974</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10136</t>
+          <t>11056</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>14379</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72748</t>
+          <t>72185</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91190</t>
+          <t>91397</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>85723</t>
+          <t>85962</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107846</t>
+          <t>108636</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>163953</t>
+          <t>166296</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>194659</t>
+          <t>194158</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,37%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>11287</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>971</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>8483</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15806</t>
+          <t>15138</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4069</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18474</t>
+          <t>18493</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18775</t>
+          <t>19169</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39454</t>
+          <t>37392</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>27171</t>
+          <t>27187</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>50651</t>
+          <t>52448</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>14070</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16087</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23915</t>
+          <t>22084</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12075</t>
+          <t>12702</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12551</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>121890</t>
+          <t>121219</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>142569</t>
+          <t>142978</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>160998</t>
+          <t>160580</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>189549</t>
+          <t>188562</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>292713</t>
+          <t>291233</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>327093</t>
+          <t>325149</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,21%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>11652</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28973</t>
+          <t>29378</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15832</t>
+          <t>15728</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>34734</t>
+          <t>34484</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24348</t>
+          <t>24922</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23361</t>
+          <t>23819</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>45563</t>
+          <t>46383</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>36666</t>
+          <t>37841</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>64691</t>
+          <t>63447</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14453</t>
+          <t>15710</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18995</t>
+          <t>19795</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>9351</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27687</t>
+          <t>27507</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -6878,7 +6878,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9681</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>432743</t>
+          <t>433418</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>473497</t>
+          <t>473366</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>482401</t>
+          <t>483610</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>535634</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>931368</t>
+          <t>929441</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>996504</t>
+          <t>991230</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,1%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13814</t>
+          <t>13687</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>33858</t>
+          <t>34370</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>29989</t>
+          <t>29806</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>55252</t>
+          <t>55770</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>47887</t>
+          <t>48572</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>81381</t>
+          <t>81685</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>42738</t>
+          <t>41795</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>72738</t>
+          <t>73249</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>115387</t>
+          <t>115155</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>157887</t>
+          <t>159663</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>163434</t>
+          <t>165694</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>217574</t>
+          <t>216403</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13182</t>
+          <t>13972</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>32361</t>
+          <t>33963</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>31199</t>
+          <t>31186</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>58573</t>
+          <t>58446</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>49309</t>
+          <t>49381</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>83470</t>
+          <t>81674</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12546</t>
+          <t>12259</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>8717</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25525</t>
+          <t>25176</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>13845</t>
+          <t>13867</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>32420</t>
+          <t>32993</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>103773</t>
+          <t>103249</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119956</t>
+          <t>120128</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>103044</t>
+          <t>103879</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>129489</t>
+          <t>129536</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>214040</t>
+          <t>212740</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>244571</t>
+          <t>244951</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,98%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8949</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25251</t>
+          <t>25956</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12660</t>
+          <t>12430</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29895</t>
+          <t>30416</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15885</t>
+          <t>16449</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23564</t>
+          <t>22848</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47842</t>
+          <t>44760</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32240</t>
+          <t>31222</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>57177</t>
+          <t>56909</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16920</t>
+          <t>15636</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>12753</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>8978</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23285</t>
+          <t>23711</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7728</t>
+          <t>7169</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>125264</t>
+          <t>124764</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143876</t>
+          <t>142857</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>139057</t>
+          <t>138877</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>168156</t>
+          <t>168059</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>271146</t>
+          <t>270963</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>307290</t>
+          <t>305960</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,66%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16365</t>
+          <t>15397</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15558</t>
+          <t>15595</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35246</t>
+          <t>34580</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22444</t>
+          <t>23027</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45951</t>
+          <t>46152</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8501</t>
+          <t>8282</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22831</t>
+          <t>21706</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19573</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42550</t>
+          <t>40885</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30768</t>
+          <t>30686</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>56854</t>
+          <t>55979</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17766</t>
+          <t>17383</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>7621</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23971</t>
+          <t>23531</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5590</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12875</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85861</t>
+          <t>84956</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101960</t>
+          <t>101911</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>82178</t>
+          <t>83912</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107212</t>
+          <t>108177</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>174787</t>
+          <t>175042</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>204471</t>
+          <t>204892</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,53%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14945</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17140</t>
+          <t>17292</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9289</t>
+          <t>9497</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27492</t>
+          <t>26744</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>17024</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15824</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35777</t>
+          <t>34855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>46397</t>
+          <t>46564</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>795</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>7366</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17141</t>
+          <t>17667</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20932</t>
+          <t>20762</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>9448</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9268</t>
+          <t>10762</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>138961</t>
+          <t>138721</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>157488</t>
+          <t>157398</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>152843</t>
+          <t>153006</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>184840</t>
+          <t>184603</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>300396</t>
+          <t>298582</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>337024</t>
+          <t>335422</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,36%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15606</t>
+          <t>16044</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13584</t>
+          <t>14388</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33128</t>
+          <t>34023</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20860</t>
+          <t>20891</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>43798</t>
+          <t>43597</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>7116</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22576</t>
+          <t>20749</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29301</t>
+          <t>30334</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>57487</t>
+          <t>55923</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>41479</t>
+          <t>40947</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>72038</t>
+          <t>71436</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>923</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>9756</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15847</t>
+          <t>15139</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20741</t>
+          <t>20674</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>471946</t>
+          <t>472970</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>507409</t>
+          <t>506860</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>507130</t>
+          <t>508571</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>562905</t>
+          <t>563315</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>992970</t>
+          <t>995354</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1059815</t>
+          <t>1060253</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,43%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21090</t>
+          <t>21484</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>41954</t>
+          <t>42537</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>55552</t>
+          <t>54878</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>90654</t>
+          <t>90706</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>83549</t>
+          <t>82450</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>124715</t>
+          <t>123771</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>35038</t>
+          <t>35216</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>61410</t>
+          <t>61378</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>107238</t>
+          <t>106620</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>154483</t>
+          <t>152778</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>149103</t>
+          <t>150172</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>200783</t>
+          <t>204051</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13756</t>
+          <t>13638</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>30993</t>
+          <t>30457</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>21601</t>
+          <t>20078</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>46110</t>
+          <t>44994</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>39528</t>
+          <t>39632</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>67937</t>
+          <t>68545</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>824</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>18940</t>
+          <t>19020</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>20647</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -11654,32 +11654,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>113170</t>
+          <t>126869</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>104603</t>
+          <t>118335</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>121262</t>
+          <t>134699</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11689,32 +11689,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>106195</t>
+          <t>113575</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>97499</t>
+          <t>104471</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113597</t>
+          <t>122308</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11724,32 +11724,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>219366</t>
+          <t>240445</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>205882</t>
+          <t>228218</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>229989</t>
+          <t>252973</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>72,0%</t>
         </is>
       </c>
     </row>
@@ -11767,32 +11767,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8867</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20198</t>
+          <t>21348</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11802,32 +11802,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26338</t>
+          <t>27778</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20776</t>
+          <t>21240</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32720</t>
+          <t>34248</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11837,32 +11837,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>39980</t>
+          <t>42250</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33010</t>
+          <t>33852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48692</t>
+          <t>51792</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -11880,32 +11880,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>14330</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9375</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20994</t>
+          <t>20833</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,32 +11915,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31124</t>
+          <t>33368</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25195</t>
+          <t>27518</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38107</t>
+          <t>40827</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>45328</t>
+          <t>47697</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37243</t>
+          <t>38662</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54111</t>
+          <t>57885</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -11993,32 +11993,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>5453</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9920</t>
+          <t>10469</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12960</t>
+          <t>13601</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9221</t>
+          <t>9544</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>18956</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,32 +12063,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18089</t>
+          <t>19055</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12826</t>
+          <t>13354</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25162</t>
+          <t>25835</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -12106,7 +12106,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>684</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -12116,12 +12116,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,32 +12141,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>309</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>679</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>146829</t>
+          <t>161808</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>146829</t>
+          <t>161808</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>146829</t>
+          <t>161808</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>177846</t>
+          <t>189541</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>177846</t>
+          <t>189541</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>177846</t>
+          <t>189541</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>324675</t>
+          <t>351350</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>324675</t>
+          <t>351350</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>324675</t>
+          <t>351350</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12336,32 +12336,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>127943</t>
+          <t>143504</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>118568</t>
+          <t>134249</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134945</t>
+          <t>151694</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12371,32 +12371,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>140366</t>
+          <t>155480</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130356</t>
+          <t>143862</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149957</t>
+          <t>166020</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,32 +12406,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>268309</t>
+          <t>298984</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>254478</t>
+          <t>284150</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>279750</t>
+          <t>312136</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,58%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7099</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11468</t>
+          <t>12380</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24848</t>
+          <t>28212</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18618</t>
+          <t>22287</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31995</t>
+          <t>36319</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,32 +12519,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>31947</t>
+          <t>35716</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25098</t>
+          <t>28078</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41173</t>
+          <t>44693</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>18855</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11599</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23996</t>
+          <t>27574</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,27 +12597,27 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>32015</t>
+          <t>35907</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25857</t>
+          <t>28463</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40326</t>
+          <t>44669</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -12632,32 +12632,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>49204</t>
+          <t>54762</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40941</t>
+          <t>45312</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59353</t>
+          <t>66072</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>7864</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12676</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,32 +12710,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17265</t>
+          <t>18029</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11979</t>
+          <t>11995</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24864</t>
+          <t>24848</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>24676</t>
+          <t>25893</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18391</t>
+          <t>19332</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33153</t>
+          <t>34807</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -12788,7 +12788,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>477</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -12798,12 +12798,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2397</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -12813,7 +12813,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,17 +12823,17 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12858,32 +12858,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>216947</t>
+          <t>240346</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>216947</t>
+          <t>240346</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>216947</t>
+          <t>240346</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>377061</t>
+          <t>418550</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>377061</t>
+          <t>418550</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>377061</t>
+          <t>418550</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13018,32 +13018,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>104476</t>
+          <t>121692</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>94732</t>
+          <t>111686</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>111965</t>
+          <t>131677</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13053,32 +13053,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>304392</t>
+          <t>111570</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>223884</t>
+          <t>101106</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>344871</t>
+          <t>121311</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13088,32 +13088,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>408867</t>
+          <t>233262</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>340388</t>
+          <t>219052</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>466075</t>
+          <t>247222</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>74,0%</t>
         </is>
       </c>
     </row>
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16815</t>
+          <t>20657</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11342</t>
+          <t>14313</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24578</t>
+          <t>29921</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,32 +13166,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>23053</t>
+          <t>26406</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>19223</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58183</t>
+          <t>34822</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>39868</t>
+          <t>47063</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13931</t>
+          <t>36061</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72760</t>
+          <t>57613</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>17,25%</t>
         </is>
       </c>
     </row>
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12659</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19354</t>
+          <t>21552</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22553</t>
+          <t>26016</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>19384</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58582</t>
+          <t>34931</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13314,32 +13314,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>35213</t>
+          <t>40028</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11355</t>
+          <t>30913</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64070</t>
+          <t>52133</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -13357,32 +13357,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>924</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7887</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13392,32 +13392,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1692</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23642</t>
+          <t>15907</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13427,32 +13427,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>12837</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23936</t>
+          <t>19735</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -13505,7 +13505,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>894</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>894</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>359663</t>
+          <t>174301</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>359663</t>
+          <t>174301</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>359663</t>
+          <t>174301</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>496615</t>
+          <t>334085</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>496615</t>
+          <t>334085</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>496615</t>
+          <t>334085</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13700,32 +13700,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>162105</t>
+          <t>170905</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>152589</t>
+          <t>160734</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>170472</t>
+          <t>179860</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13735,32 +13735,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>170934</t>
+          <t>181376</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>158859</t>
+          <t>167486</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>181621</t>
+          <t>193613</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13770,32 +13770,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>333039</t>
+          <t>352281</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>318211</t>
+          <t>335409</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>347165</t>
+          <t>368745</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -13813,32 +13813,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>17958</t>
+          <t>18265</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>12937</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25597</t>
+          <t>26187</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>43634</t>
+          <t>46156</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35063</t>
+          <t>37116</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>52987</t>
+          <t>58073</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>61593</t>
+          <t>64421</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>51313</t>
+          <t>53477</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>72783</t>
+          <t>76734</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -13926,32 +13926,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20950</t>
+          <t>21424</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14703</t>
+          <t>15297</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28172</t>
+          <t>29415</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13961,22 +13961,22 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>41448</t>
+          <t>45557</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>34292</t>
+          <t>36733</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50332</t>
+          <t>55015</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,27 +13996,27 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>62398</t>
+          <t>66981</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>51774</t>
+          <t>55406</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>74754</t>
+          <t>79413</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -14039,32 +14039,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14074,32 +14074,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>17942</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>11737</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22549</t>
+          <t>25850</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>18913</t>
+          <t>21783</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26878</t>
+          <t>30921</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -14187,32 +14187,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>452</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5698</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14222,17 +14222,17 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>455</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14247,7 +14247,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>204424</t>
+          <t>214436</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>204424</t>
+          <t>214436</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>204424</t>
+          <t>214436</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>273353</t>
+          <t>292947</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>273353</t>
+          <t>292947</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>273353</t>
+          <t>292947</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>477778</t>
+          <t>507383</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>477778</t>
+          <t>507383</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>477778</t>
+          <t>507383</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14382,32 +14382,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>507695</t>
+          <t>562969</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>489981</t>
+          <t>545975</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>524257</t>
+          <t>580634</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14417,32 +14417,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>721887</t>
+          <t>562001</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>638243</t>
+          <t>538330</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>867480</t>
+          <t>584002</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14452,32 +14452,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1229582</t>
+          <t>1124971</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1155685</t>
+          <t>1092146</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1391367</t>
+          <t>1152956</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>71,55%</t>
         </is>
       </c>
     </row>
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>55515</t>
+          <t>60899</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>45396</t>
+          <t>50180</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>69212</t>
+          <t>74025</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,32 +14530,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>117873</t>
+          <t>128551</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>59944</t>
+          <t>113616</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>153666</t>
+          <t>144840</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,32 +14565,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>173388</t>
+          <t>189450</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>111567</t>
+          <t>168733</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>207125</t>
+          <t>209250</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -14608,32 +14608,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>65003</t>
+          <t>68621</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>54274</t>
+          <t>56311</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>77577</t>
+          <t>82486</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14643,32 +14643,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>127140</t>
+          <t>140848</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>67004</t>
+          <t>124490</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>165246</t>
+          <t>156488</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14678,32 +14678,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>192143</t>
+          <t>209469</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>124199</t>
+          <t>189614</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>228459</t>
+          <t>232060</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -14721,32 +14721,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>18953</t>
+          <t>20581</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12790</t>
+          <t>14009</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27204</t>
+          <t>28644</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14756,32 +14756,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>54654</t>
+          <t>58986</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>27247</t>
+          <t>48439</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>72920</t>
+          <t>71615</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,32 +14791,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>73607</t>
+          <t>79567</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>48494</t>
+          <t>66005</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>91116</t>
+          <t>93303</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -14834,22 +14834,22 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>340</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -14859,7 +14859,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2825</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>11209</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7910</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11732</t>
+          <t>12704</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>648320</t>
+          <t>714232</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>648320</t>
+          <t>714232</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>648320</t>
+          <t>714232</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1027810</t>
+          <t>897135</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1027810</t>
+          <t>897135</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1027810</t>
+          <t>897135</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1676130</t>
+          <t>1611368</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1676130</t>
+          <t>1611368</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1676130</t>
+          <t>1611368</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
